--- a/matcha_library.xlsx
+++ b/matcha_library.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data" sheetId="1" r:id="R53d8c48c05f448e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용안내" sheetId="2" r:id="R0e1d5ade36954c1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data" sheetId="1" r:id="R1e50be06358041d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용안내" sheetId="2" r:id="Re92b54df690d408f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -116,27 +116,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchaData" displayName="MatchaData" ref="A1:S37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="19">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchaData" displayName="MatchaData" ref="A1:Q37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="17">
     <x:tableColumn id="1" name="sample_id"/>
     <x:tableColumn id="2" name="lot_id"/>
     <x:tableColumn id="3" name="origin"/>
     <x:tableColumn id="4" name="cultivar"/>
     <x:tableColumn id="5" name="harvest_date"/>
     <x:tableColumn id="6" name="data_type"/>
-    <x:tableColumn id="7" name="protocol_id"/>
-    <x:tableColumn id="8" name="unit"/>
-    <x:tableColumn id="9" name="glutamate"/>
-    <x:tableColumn id="10" name="glutamine"/>
-    <x:tableColumn id="11" name="theanine"/>
-    <x:tableColumn id="12" name="caffeine"/>
-    <x:tableColumn id="13" name="umami"/>
-    <x:tableColumn id="14" name="sweetness"/>
-    <x:tableColumn id="15" name="bitterness"/>
-    <x:tableColumn id="16" name="astringency"/>
-    <x:tableColumn id="17" name="panel_n"/>
-    <x:tableColumn id="18" name="sensory_repeats"/>
-    <x:tableColumn id="19" name="notes"/>
+    <x:tableColumn id="7" name="unit"/>
+    <x:tableColumn id="8" name="glutamate"/>
+    <x:tableColumn id="9" name="theanine"/>
+    <x:tableColumn id="10" name="caffeine"/>
+    <x:tableColumn id="11" name="umami"/>
+    <x:tableColumn id="12" name="sweetness"/>
+    <x:tableColumn id="13" name="bitterness"/>
+    <x:tableColumn id="14" name="astringency"/>
+    <x:tableColumn id="15" name="panel_n"/>
+    <x:tableColumn id="16" name="sensory_repeats"/>
+    <x:tableColumn id="17" name="notes"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -356,9 +354,7 @@
     <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="16" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="16" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="16" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="55" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="55" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
@@ -381,42 +377,36 @@
         <x:v>data_type</x:v>
       </x:c>
       <x:c r="G1" s="4" t="str">
-        <x:v>protocol_id</x:v>
+        <x:v>unit</x:v>
       </x:c>
       <x:c r="H1" s="4" t="str">
-        <x:v>unit</x:v>
+        <x:v>glutamate</x:v>
       </x:c>
       <x:c r="I1" s="4" t="str">
-        <x:v>glutamate</x:v>
+        <x:v>theanine</x:v>
       </x:c>
       <x:c r="J1" s="4" t="str">
-        <x:v>glutamine</x:v>
+        <x:v>caffeine</x:v>
       </x:c>
       <x:c r="K1" s="4" t="str">
-        <x:v>theanine</x:v>
+        <x:v>umami</x:v>
       </x:c>
       <x:c r="L1" s="4" t="str">
-        <x:v>caffeine</x:v>
+        <x:v>sweetness</x:v>
       </x:c>
       <x:c r="M1" s="4" t="str">
-        <x:v>umami</x:v>
+        <x:v>bitterness</x:v>
       </x:c>
       <x:c r="N1" s="4" t="str">
-        <x:v>sweetness</x:v>
+        <x:v>astringency</x:v>
       </x:c>
       <x:c r="O1" s="4" t="str">
-        <x:v>bitterness</x:v>
+        <x:v>panel_n</x:v>
       </x:c>
       <x:c r="P1" s="4" t="str">
-        <x:v>astringency</x:v>
+        <x:v>sensory_repeats</x:v>
       </x:c>
       <x:c r="Q1" s="4" t="str">
-        <x:v>panel_n</x:v>
-      </x:c>
-      <x:c r="R1" s="4" t="str">
-        <x:v>sensory_repeats</x:v>
-      </x:c>
-      <x:c r="S1" s="4" t="str">
         <x:v>notes</x:v>
       </x:c>
     </x:row>
@@ -437,45 +427,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F2" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G2" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="n">
+        <x:v>3.03</x:v>
       </x:c>
       <x:c r="I2" s="7" t="n">
-        <x:v>3.03</x:v>
+        <x:v>16.47</x:v>
       </x:c>
       <x:c r="J2" s="7" t="n">
-        <x:v>1.24</x:v>
+        <x:v>26.96</x:v>
       </x:c>
       <x:c r="K2" s="7" t="n">
-        <x:v>16.47</x:v>
+        <x:v>4.26</x:v>
       </x:c>
       <x:c r="L2" s="7" t="n">
-        <x:v>26.96</x:v>
+        <x:v>2.03</x:v>
       </x:c>
       <x:c r="M2" s="7" t="n">
-        <x:v>4.26</x:v>
+        <x:v>2.97</x:v>
       </x:c>
       <x:c r="N2" s="7" t="n">
-        <x:v>2.03</x:v>
-      </x:c>
-      <x:c r="O2" s="7" t="n">
-        <x:v>2.97</x:v>
-      </x:c>
-      <x:c r="P2" s="7" t="n">
         <x:v>4.23</x:v>
       </x:c>
-      <x:c r="Q2" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R2" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S2" s="1" t="str">
+      <x:c r="O2" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P2" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q2" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -496,45 +480,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F3" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G3" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H3" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="n">
+        <x:v>1.43</x:v>
       </x:c>
       <x:c r="I3" s="7" t="n">
-        <x:v>1.43</x:v>
+        <x:v>15.84</x:v>
       </x:c>
       <x:c r="J3" s="7" t="n">
-        <x:v>1.06</x:v>
+        <x:v>38.55</x:v>
       </x:c>
       <x:c r="K3" s="7" t="n">
-        <x:v>15.84</x:v>
+        <x:v>2.37</x:v>
       </x:c>
       <x:c r="L3" s="7" t="n">
-        <x:v>38.55</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="M3" s="7" t="n">
-        <x:v>2.37</x:v>
+        <x:v>4.82</x:v>
       </x:c>
       <x:c r="N3" s="7" t="n">
-        <x:v>2.4</x:v>
-      </x:c>
-      <x:c r="O3" s="7" t="n">
-        <x:v>4.82</x:v>
-      </x:c>
-      <x:c r="P3" s="7" t="n">
         <x:v>3.54</x:v>
       </x:c>
-      <x:c r="Q3" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R3" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S3" s="1" t="str">
+      <x:c r="O3" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P3" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q3" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -555,45 +533,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F4" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G4" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H4" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H4" s="7" t="n">
+        <x:v>1.64</x:v>
       </x:c>
       <x:c r="I4" s="7" t="n">
-        <x:v>1.64</x:v>
+        <x:v>24.29</x:v>
       </x:c>
       <x:c r="J4" s="7" t="n">
-        <x:v>2.47</x:v>
+        <x:v>24.03</x:v>
       </x:c>
       <x:c r="K4" s="7" t="n">
-        <x:v>24.29</x:v>
+        <x:v>3.4</x:v>
       </x:c>
       <x:c r="L4" s="7" t="n">
-        <x:v>24.03</x:v>
+        <x:v>1.97</x:v>
       </x:c>
       <x:c r="M4" s="7" t="n">
-        <x:v>3.4</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="N4" s="7" t="n">
-        <x:v>1.97</x:v>
-      </x:c>
-      <x:c r="O4" s="7" t="n">
-        <x:v>2.64</x:v>
-      </x:c>
-      <x:c r="P4" s="7" t="n">
         <x:v>1.88</x:v>
       </x:c>
-      <x:c r="Q4" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R4" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S4" s="1" t="str">
+      <x:c r="O4" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P4" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q4" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -614,45 +586,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G5" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H5" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H5" s="7" t="n">
+        <x:v>4.6</x:v>
       </x:c>
       <x:c r="I5" s="7" t="n">
-        <x:v>4.6</x:v>
+        <x:v>7.54</x:v>
       </x:c>
       <x:c r="J5" s="7" t="n">
-        <x:v>1.5</x:v>
+        <x:v>39.08</x:v>
       </x:c>
       <x:c r="K5" s="7" t="n">
-        <x:v>7.54</x:v>
+        <x:v>3.19</x:v>
       </x:c>
       <x:c r="L5" s="7" t="n">
-        <x:v>39.08</x:v>
+        <x:v>1.37</x:v>
       </x:c>
       <x:c r="M5" s="7" t="n">
-        <x:v>3.19</x:v>
+        <x:v>5.56</x:v>
       </x:c>
       <x:c r="N5" s="7" t="n">
-        <x:v>1.37</x:v>
-      </x:c>
-      <x:c r="O5" s="7" t="n">
-        <x:v>5.56</x:v>
-      </x:c>
-      <x:c r="P5" s="7" t="n">
         <x:v>2.28</x:v>
       </x:c>
-      <x:c r="Q5" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R5" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S5" s="1" t="str">
+      <x:c r="O5" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P5" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q5" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -673,45 +639,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F6" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G6" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H6" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H6" s="7" t="n">
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="I6" s="7" t="n">
-        <x:v>2.4</x:v>
+        <x:v>12.49</x:v>
       </x:c>
       <x:c r="J6" s="7" t="n">
-        <x:v>1.79</x:v>
+        <x:v>30.92</x:v>
       </x:c>
       <x:c r="K6" s="7" t="n">
-        <x:v>12.49</x:v>
+        <x:v>3.26</x:v>
       </x:c>
       <x:c r="L6" s="7" t="n">
-        <x:v>30.92</x:v>
+        <x:v>1.28</x:v>
       </x:c>
       <x:c r="M6" s="7" t="n">
-        <x:v>3.26</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="N6" s="7" t="n">
-        <x:v>1.28</x:v>
-      </x:c>
-      <x:c r="O6" s="7" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="P6" s="7" t="n">
         <x:v>4.06</x:v>
       </x:c>
-      <x:c r="Q6" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R6" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S6" s="1" t="str">
+      <x:c r="O6" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P6" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q6" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -732,45 +692,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F7" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G7" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H7" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H7" s="7" t="n">
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="I7" s="7" t="n">
-        <x:v>3.3</x:v>
+        <x:v>7.97</x:v>
       </x:c>
       <x:c r="J7" s="7" t="n">
-        <x:v>1.25</x:v>
+        <x:v>38.98</x:v>
       </x:c>
       <x:c r="K7" s="7" t="n">
-        <x:v>7.97</x:v>
+        <x:v>3.38</x:v>
       </x:c>
       <x:c r="L7" s="7" t="n">
-        <x:v>38.98</x:v>
+        <x:v>1.88</x:v>
       </x:c>
       <x:c r="M7" s="7" t="n">
-        <x:v>3.38</x:v>
+        <x:v>5.29</x:v>
       </x:c>
       <x:c r="N7" s="7" t="n">
-        <x:v>1.88</x:v>
-      </x:c>
-      <x:c r="O7" s="7" t="n">
-        <x:v>5.29</x:v>
-      </x:c>
-      <x:c r="P7" s="7" t="n">
         <x:v>2.98</x:v>
       </x:c>
-      <x:c r="Q7" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R7" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S7" s="1" t="str">
+      <x:c r="O7" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P7" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q7" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -791,45 +745,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F8" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G8" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H8" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H8" s="7" t="n">
+        <x:v>1.77</x:v>
       </x:c>
       <x:c r="I8" s="7" t="n">
-        <x:v>1.77</x:v>
+        <x:v>17.79</x:v>
       </x:c>
       <x:c r="J8" s="7" t="n">
-        <x:v>3.26</x:v>
+        <x:v>39.59</x:v>
       </x:c>
       <x:c r="K8" s="7" t="n">
-        <x:v>17.79</x:v>
+        <x:v>2.75</x:v>
       </x:c>
       <x:c r="L8" s="7" t="n">
-        <x:v>39.59</x:v>
+        <x:v>1.72</x:v>
       </x:c>
       <x:c r="M8" s="7" t="n">
-        <x:v>2.75</x:v>
+        <x:v>4.81</x:v>
       </x:c>
       <x:c r="N8" s="7" t="n">
-        <x:v>1.72</x:v>
-      </x:c>
-      <x:c r="O8" s="7" t="n">
-        <x:v>4.81</x:v>
-      </x:c>
-      <x:c r="P8" s="7" t="n">
         <x:v>2.35</x:v>
       </x:c>
-      <x:c r="Q8" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R8" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S8" s="1" t="str">
+      <x:c r="O8" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P8" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q8" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -850,45 +798,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F9" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G9" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H9" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H9" s="7" t="n">
+        <x:v>4.57</x:v>
       </x:c>
       <x:c r="I9" s="7" t="n">
-        <x:v>4.57</x:v>
+        <x:v>8.44</x:v>
       </x:c>
       <x:c r="J9" s="7" t="n">
-        <x:v>2.97</x:v>
+        <x:v>20.07</x:v>
       </x:c>
       <x:c r="K9" s="7" t="n">
-        <x:v>8.44</x:v>
+        <x:v>4.03</x:v>
       </x:c>
       <x:c r="L9" s="7" t="n">
-        <x:v>20.07</x:v>
+        <x:v>1.61</x:v>
       </x:c>
       <x:c r="M9" s="7" t="n">
-        <x:v>4.03</x:v>
+        <x:v>2.59</x:v>
       </x:c>
       <x:c r="N9" s="7" t="n">
-        <x:v>1.61</x:v>
-      </x:c>
-      <x:c r="O9" s="7" t="n">
         <x:v>2.59</x:v>
       </x:c>
-      <x:c r="P9" s="7" t="n">
-        <x:v>2.59</x:v>
-      </x:c>
-      <x:c r="Q9" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R9" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S9" s="1" t="str">
+      <x:c r="O9" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P9" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q9" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -909,45 +851,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F10" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G10" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H10" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H10" s="7" t="n">
+        <x:v>1.72</x:v>
       </x:c>
       <x:c r="I10" s="7" t="n">
-        <x:v>1.72</x:v>
+        <x:v>18.68</x:v>
       </x:c>
       <x:c r="J10" s="7" t="n">
-        <x:v>2.24</x:v>
+        <x:v>31.84</x:v>
       </x:c>
       <x:c r="K10" s="7" t="n">
-        <x:v>18.68</x:v>
+        <x:v>3.17</x:v>
       </x:c>
       <x:c r="L10" s="7" t="n">
-        <x:v>31.84</x:v>
+        <x:v>1.78</x:v>
       </x:c>
       <x:c r="M10" s="7" t="n">
-        <x:v>3.17</x:v>
+        <x:v>3.35</x:v>
       </x:c>
       <x:c r="N10" s="7" t="n">
-        <x:v>1.78</x:v>
-      </x:c>
-      <x:c r="O10" s="7" t="n">
-        <x:v>3.35</x:v>
-      </x:c>
-      <x:c r="P10" s="7" t="n">
         <x:v>4.13</x:v>
       </x:c>
-      <x:c r="Q10" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R10" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S10" s="1" t="str">
+      <x:c r="O10" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P10" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q10" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -968,45 +904,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F11" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G11" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H11" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H11" s="7" t="n">
+        <x:v>4.94</x:v>
       </x:c>
       <x:c r="I11" s="7" t="n">
-        <x:v>4.94</x:v>
+        <x:v>21.54</x:v>
       </x:c>
       <x:c r="J11" s="7" t="n">
-        <x:v>2.75</x:v>
+        <x:v>35.5</x:v>
       </x:c>
       <x:c r="K11" s="7" t="n">
-        <x:v>21.54</x:v>
+        <x:v>5.44</x:v>
       </x:c>
       <x:c r="L11" s="7" t="n">
-        <x:v>35.5</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="M11" s="7" t="n">
-        <x:v>5.44</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="N11" s="7" t="n">
-        <x:v>2.3</x:v>
-      </x:c>
-      <x:c r="O11" s="7" t="n">
-        <x:v>3.75</x:v>
-      </x:c>
-      <x:c r="P11" s="7" t="n">
         <x:v>3.96</x:v>
       </x:c>
-      <x:c r="Q11" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R11" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S11" s="1" t="str">
+      <x:c r="O11" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P11" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q11" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -1027,45 +957,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F12" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G12" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H12" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H12" s="7" t="n">
+        <x:v>5.82</x:v>
       </x:c>
       <x:c r="I12" s="7" t="n">
+        <x:v>26.74</x:v>
+      </x:c>
+      <x:c r="J12" s="7" t="n">
+        <x:v>21.52</x:v>
+      </x:c>
+      <x:c r="K12" s="7" t="n">
         <x:v>5.82</x:v>
       </x:c>
-      <x:c r="J12" s="7" t="n">
-        <x:v>2.14</x:v>
-      </x:c>
-      <x:c r="K12" s="7" t="n">
-        <x:v>26.74</x:v>
-      </x:c>
       <x:c r="L12" s="7" t="n">
-        <x:v>21.52</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="M12" s="7" t="n">
-        <x:v>5.82</x:v>
+        <x:v>1.73</x:v>
       </x:c>
       <x:c r="N12" s="7" t="n">
-        <x:v>2.64</x:v>
-      </x:c>
-      <x:c r="O12" s="7" t="n">
-        <x:v>1.73</x:v>
-      </x:c>
-      <x:c r="P12" s="7" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="Q12" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R12" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S12" s="1" t="str">
+      <x:c r="O12" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P12" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q12" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -1086,45 +1010,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F13" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G13" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H13" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H13" s="7" t="n">
+        <x:v>4.08</x:v>
       </x:c>
       <x:c r="I13" s="7" t="n">
-        <x:v>4.08</x:v>
+        <x:v>31.1</x:v>
       </x:c>
       <x:c r="J13" s="7" t="n">
-        <x:v>2.1</x:v>
+        <x:v>19.61</x:v>
       </x:c>
       <x:c r="K13" s="7" t="n">
-        <x:v>31.1</x:v>
+        <x:v>5.82</x:v>
       </x:c>
       <x:c r="L13" s="7" t="n">
-        <x:v>19.61</x:v>
+        <x:v>3.11</x:v>
       </x:c>
       <x:c r="M13" s="7" t="n">
-        <x:v>5.82</x:v>
+        <x:v>1.27</x:v>
       </x:c>
       <x:c r="N13" s="7" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="O13" s="7" t="n">
-        <x:v>1.27</x:v>
-      </x:c>
-      <x:c r="P13" s="7" t="n">
         <x:v>2.65</x:v>
       </x:c>
-      <x:c r="Q13" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R13" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S13" s="1" t="str">
+      <x:c r="O13" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P13" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q13" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -1145,45 +1063,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F14" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G14" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H14" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H14" s="7" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>9.08</x:v>
       </x:c>
       <x:c r="J14" s="7" t="n">
-        <x:v>2.5</x:v>
+        <x:v>31.48</x:v>
       </x:c>
       <x:c r="K14" s="7" t="n">
-        <x:v>9.08</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="L14" s="7" t="n">
-        <x:v>31.48</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="M14" s="7" t="n">
-        <x:v>1.8</x:v>
+        <x:v>4.65</x:v>
       </x:c>
       <x:c r="N14" s="7" t="n">
-        <x:v>1.1</x:v>
-      </x:c>
-      <x:c r="O14" s="7" t="n">
-        <x:v>4.65</x:v>
-      </x:c>
-      <x:c r="P14" s="7" t="n">
         <x:v>2.93</x:v>
       </x:c>
-      <x:c r="Q14" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R14" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S14" s="1" t="str">
+      <x:c r="O14" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P14" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q14" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -1204,45 +1116,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F15" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G15" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H15" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H15" s="7" t="n">
+        <x:v>2.84</x:v>
       </x:c>
       <x:c r="I15" s="7" t="n">
-        <x:v>2.84</x:v>
+        <x:v>17.58</x:v>
       </x:c>
       <x:c r="J15" s="7" t="n">
-        <x:v>1.08</x:v>
+        <x:v>18.67</x:v>
       </x:c>
       <x:c r="K15" s="7" t="n">
-        <x:v>17.58</x:v>
+        <x:v>3.51</x:v>
       </x:c>
       <x:c r="L15" s="7" t="n">
-        <x:v>18.67</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="M15" s="7" t="n">
-        <x:v>3.51</x:v>
+        <x:v>2.42</x:v>
       </x:c>
       <x:c r="N15" s="7" t="n">
-        <x:v>1.75</x:v>
-      </x:c>
-      <x:c r="O15" s="7" t="n">
-        <x:v>2.42</x:v>
-      </x:c>
-      <x:c r="P15" s="7" t="n">
         <x:v>2.95</x:v>
       </x:c>
-      <x:c r="Q15" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R15" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S15" s="1" t="str">
+      <x:c r="O15" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P15" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q15" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -1263,45 +1169,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F16" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G16" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H16" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H16" s="7" t="n">
+        <x:v>2.77</x:v>
       </x:c>
       <x:c r="I16" s="7" t="n">
-        <x:v>2.77</x:v>
+        <x:v>22.34</x:v>
       </x:c>
       <x:c r="J16" s="7" t="n">
-        <x:v>1.87</x:v>
+        <x:v>23.8</x:v>
       </x:c>
       <x:c r="K16" s="7" t="n">
-        <x:v>22.34</x:v>
+        <x:v>4.73</x:v>
       </x:c>
       <x:c r="L16" s="7" t="n">
-        <x:v>23.8</x:v>
+        <x:v>1.92</x:v>
       </x:c>
       <x:c r="M16" s="7" t="n">
-        <x:v>4.73</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="N16" s="7" t="n">
-        <x:v>1.92</x:v>
-      </x:c>
-      <x:c r="O16" s="7" t="n">
-        <x:v>2.11</x:v>
-      </x:c>
-      <x:c r="P16" s="7" t="n">
         <x:v>3.28</x:v>
       </x:c>
-      <x:c r="Q16" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R16" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S16" s="1" t="str">
+      <x:c r="O16" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P16" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q16" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -1322,45 +1222,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F17" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G17" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H17" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H17" s="7" t="n">
+        <x:v>4.21</x:v>
       </x:c>
       <x:c r="I17" s="7" t="n">
-        <x:v>4.21</x:v>
+        <x:v>10.35</x:v>
       </x:c>
       <x:c r="J17" s="7" t="n">
-        <x:v>1.94</x:v>
+        <x:v>39.73</x:v>
       </x:c>
       <x:c r="K17" s="7" t="n">
-        <x:v>10.35</x:v>
+        <x:v>3.54</x:v>
       </x:c>
       <x:c r="L17" s="7" t="n">
-        <x:v>39.73</x:v>
+        <x:v>2.47</x:v>
       </x:c>
       <x:c r="M17" s="7" t="n">
-        <x:v>3.54</x:v>
+        <x:v>4.99</x:v>
       </x:c>
       <x:c r="N17" s="7" t="n">
-        <x:v>2.47</x:v>
-      </x:c>
-      <x:c r="O17" s="7" t="n">
-        <x:v>4.99</x:v>
-      </x:c>
-      <x:c r="P17" s="7" t="n">
         <x:v>4.07</x:v>
       </x:c>
-      <x:c r="Q17" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R17" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S17" s="1" t="str">
+      <x:c r="O17" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P17" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q17" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -1381,45 +1275,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F18" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G18" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H18" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H18" s="7" t="n">
+        <x:v>3.62</x:v>
       </x:c>
       <x:c r="I18" s="7" t="n">
-        <x:v>3.62</x:v>
+        <x:v>16.11</x:v>
       </x:c>
       <x:c r="J18" s="7" t="n">
-        <x:v>0.48</x:v>
+        <x:v>28.05</x:v>
       </x:c>
       <x:c r="K18" s="7" t="n">
-        <x:v>16.11</x:v>
+        <x:v>4.35</x:v>
       </x:c>
       <x:c r="L18" s="7" t="n">
-        <x:v>28.05</x:v>
+        <x:v>2.29</x:v>
       </x:c>
       <x:c r="M18" s="7" t="n">
-        <x:v>4.35</x:v>
+        <x:v>3.77</x:v>
       </x:c>
       <x:c r="N18" s="7" t="n">
-        <x:v>2.29</x:v>
-      </x:c>
-      <x:c r="O18" s="7" t="n">
-        <x:v>3.77</x:v>
-      </x:c>
-      <x:c r="P18" s="7" t="n">
         <x:v>3.72</x:v>
       </x:c>
-      <x:c r="Q18" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R18" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S18" s="1" t="str">
+      <x:c r="O18" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P18" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q18" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -1440,45 +1328,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F19" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G19" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H19" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H19" s="7" t="n">
+        <x:v>4.91</x:v>
       </x:c>
       <x:c r="I19" s="7" t="n">
-        <x:v>4.91</x:v>
+        <x:v>8.55</x:v>
       </x:c>
       <x:c r="J19" s="7" t="n">
-        <x:v>1.79</x:v>
+        <x:v>32.3</x:v>
       </x:c>
       <x:c r="K19" s="7" t="n">
-        <x:v>8.55</x:v>
+        <x:v>4.52</x:v>
       </x:c>
       <x:c r="L19" s="7" t="n">
-        <x:v>32.3</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="M19" s="7" t="n">
-        <x:v>4.52</x:v>
+        <x:v>4.04</x:v>
       </x:c>
       <x:c r="N19" s="7" t="n">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="O19" s="7" t="n">
-        <x:v>4.04</x:v>
-      </x:c>
-      <x:c r="P19" s="7" t="n">
         <x:v>2.47</x:v>
       </x:c>
-      <x:c r="Q19" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R19" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S19" s="1" t="str">
+      <x:c r="O19" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P19" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q19" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -1499,45 +1381,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F20" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G20" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H20" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H20" s="7" t="n">
+        <x:v>3.55</x:v>
       </x:c>
       <x:c r="I20" s="7" t="n">
-        <x:v>3.55</x:v>
+        <x:v>31.73</x:v>
       </x:c>
       <x:c r="J20" s="7" t="n">
-        <x:v>0.87</x:v>
+        <x:v>21.64</x:v>
       </x:c>
       <x:c r="K20" s="7" t="n">
-        <x:v>31.73</x:v>
+        <x:v>5.43</x:v>
       </x:c>
       <x:c r="L20" s="7" t="n">
-        <x:v>21.64</x:v>
+        <x:v>3.37</x:v>
       </x:c>
       <x:c r="M20" s="7" t="n">
-        <x:v>5.43</x:v>
+        <x:v>1.68</x:v>
       </x:c>
       <x:c r="N20" s="7" t="n">
-        <x:v>3.37</x:v>
-      </x:c>
-      <x:c r="O20" s="7" t="n">
-        <x:v>1.68</x:v>
-      </x:c>
-      <x:c r="P20" s="7" t="n">
         <x:v>3.17</x:v>
       </x:c>
-      <x:c r="Q20" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R20" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S20" s="1" t="str">
+      <x:c r="O20" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P20" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q20" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -1558,45 +1434,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F21" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G21" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H21" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H21" s="7" t="n">
+        <x:v>4.57</x:v>
       </x:c>
       <x:c r="I21" s="7" t="n">
-        <x:v>4.57</x:v>
+        <x:v>12.87</x:v>
       </x:c>
       <x:c r="J21" s="7" t="n">
-        <x:v>3.28</x:v>
+        <x:v>26.71</x:v>
       </x:c>
       <x:c r="K21" s="7" t="n">
-        <x:v>12.87</x:v>
+        <x:v>4.84</x:v>
       </x:c>
       <x:c r="L21" s="7" t="n">
-        <x:v>26.71</x:v>
+        <x:v>2.03</x:v>
       </x:c>
       <x:c r="M21" s="7" t="n">
-        <x:v>4.84</x:v>
+        <x:v>3.13</x:v>
       </x:c>
       <x:c r="N21" s="7" t="n">
-        <x:v>2.03</x:v>
-      </x:c>
-      <x:c r="O21" s="7" t="n">
-        <x:v>3.13</x:v>
-      </x:c>
-      <x:c r="P21" s="7" t="n">
         <x:v>1.87</x:v>
       </x:c>
-      <x:c r="Q21" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R21" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S21" s="1" t="str">
+      <x:c r="O21" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P21" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q21" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -1617,45 +1487,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F22" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G22" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H22" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H22" s="7" t="n">
+        <x:v>4.58</x:v>
       </x:c>
       <x:c r="I22" s="7" t="n">
-        <x:v>4.58</x:v>
+        <x:v>10.9</x:v>
       </x:c>
       <x:c r="J22" s="7" t="n">
-        <x:v>1.82</x:v>
+        <x:v>30.35</x:v>
       </x:c>
       <x:c r="K22" s="7" t="n">
-        <x:v>10.9</x:v>
+        <x:v>4.17</x:v>
       </x:c>
       <x:c r="L22" s="7" t="n">
-        <x:v>30.35</x:v>
+        <x:v>2.26</x:v>
       </x:c>
       <x:c r="M22" s="7" t="n">
-        <x:v>4.17</x:v>
+        <x:v>4.02</x:v>
       </x:c>
       <x:c r="N22" s="7" t="n">
-        <x:v>2.26</x:v>
-      </x:c>
-      <x:c r="O22" s="7" t="n">
-        <x:v>4.02</x:v>
-      </x:c>
-      <x:c r="P22" s="7" t="n">
         <x:v>2.74</x:v>
       </x:c>
-      <x:c r="Q22" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R22" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S22" s="1" t="str">
+      <x:c r="O22" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P22" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q22" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -1676,45 +1540,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F23" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G23" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H23" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H23" s="7" t="n">
+        <x:v>4.28</x:v>
       </x:c>
       <x:c r="I23" s="7" t="n">
-        <x:v>4.28</x:v>
+        <x:v>9.27</x:v>
       </x:c>
       <x:c r="J23" s="7" t="n">
-        <x:v>2.82</x:v>
+        <x:v>31.09</x:v>
       </x:c>
       <x:c r="K23" s="7" t="n">
-        <x:v>9.27</x:v>
+        <x:v>3.6</x:v>
       </x:c>
       <x:c r="L23" s="7" t="n">
-        <x:v>31.09</x:v>
+        <x:v>2.17</x:v>
       </x:c>
       <x:c r="M23" s="7" t="n">
-        <x:v>3.6</x:v>
+        <x:v>4.67</x:v>
       </x:c>
       <x:c r="N23" s="7" t="n">
-        <x:v>2.17</x:v>
-      </x:c>
-      <x:c r="O23" s="7" t="n">
-        <x:v>4.67</x:v>
-      </x:c>
-      <x:c r="P23" s="7" t="n">
         <x:v>3.64</x:v>
       </x:c>
-      <x:c r="Q23" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R23" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S23" s="1" t="str">
+      <x:c r="O23" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P23" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q23" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -1735,45 +1593,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F24" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G24" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H24" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H24" s="7" t="n">
+        <x:v>1.85</x:v>
       </x:c>
       <x:c r="I24" s="7" t="n">
-        <x:v>1.85</x:v>
+        <x:v>19.95</x:v>
       </x:c>
       <x:c r="J24" s="7" t="n">
-        <x:v>1.2</x:v>
+        <x:v>26.03</x:v>
       </x:c>
       <x:c r="K24" s="7" t="n">
-        <x:v>19.95</x:v>
+        <x:v>3.62</x:v>
       </x:c>
       <x:c r="L24" s="7" t="n">
-        <x:v>26.03</x:v>
+        <x:v>2.62</x:v>
       </x:c>
       <x:c r="M24" s="7" t="n">
-        <x:v>3.62</x:v>
+        <x:v>2.67</x:v>
       </x:c>
       <x:c r="N24" s="7" t="n">
-        <x:v>2.62</x:v>
-      </x:c>
-      <x:c r="O24" s="7" t="n">
-        <x:v>2.67</x:v>
-      </x:c>
-      <x:c r="P24" s="7" t="n">
         <x:v>2.09</x:v>
       </x:c>
-      <x:c r="Q24" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R24" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S24" s="1" t="str">
+      <x:c r="O24" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P24" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q24" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -1794,45 +1646,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F25" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G25" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H25" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H25" s="7" t="n">
+        <x:v>4.49</x:v>
       </x:c>
       <x:c r="I25" s="7" t="n">
-        <x:v>4.49</x:v>
+        <x:v>26.08</x:v>
       </x:c>
       <x:c r="J25" s="7" t="n">
-        <x:v>2.26</x:v>
+        <x:v>32.03</x:v>
       </x:c>
       <x:c r="K25" s="7" t="n">
-        <x:v>26.08</x:v>
+        <x:v>4.96</x:v>
       </x:c>
       <x:c r="L25" s="7" t="n">
-        <x:v>32.03</x:v>
+        <x:v>2.77</x:v>
       </x:c>
       <x:c r="M25" s="7" t="n">
-        <x:v>4.96</x:v>
+        <x:v>3.01</x:v>
       </x:c>
       <x:c r="N25" s="7" t="n">
-        <x:v>2.77</x:v>
-      </x:c>
-      <x:c r="O25" s="7" t="n">
-        <x:v>3.01</x:v>
-      </x:c>
-      <x:c r="P25" s="7" t="n">
         <x:v>3.31</x:v>
       </x:c>
-      <x:c r="Q25" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R25" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S25" s="1" t="str">
+      <x:c r="O25" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P25" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q25" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -1853,45 +1699,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F26" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G26" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H26" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H26" s="7" t="n">
+        <x:v>4.32</x:v>
       </x:c>
       <x:c r="I26" s="7" t="n">
-        <x:v>4.32</x:v>
+        <x:v>17.36</x:v>
       </x:c>
       <x:c r="J26" s="7" t="n">
-        <x:v>2.18</x:v>
+        <x:v>35.72</x:v>
       </x:c>
       <x:c r="K26" s="7" t="n">
-        <x:v>17.36</x:v>
+        <x:v>3.89</x:v>
       </x:c>
       <x:c r="L26" s="7" t="n">
-        <x:v>35.72</x:v>
+        <x:v>2.31</x:v>
       </x:c>
       <x:c r="M26" s="7" t="n">
-        <x:v>3.89</x:v>
+        <x:v>4.02</x:v>
       </x:c>
       <x:c r="N26" s="7" t="n">
-        <x:v>2.31</x:v>
-      </x:c>
-      <x:c r="O26" s="7" t="n">
-        <x:v>4.02</x:v>
-      </x:c>
-      <x:c r="P26" s="7" t="n">
         <x:v>2.86</x:v>
       </x:c>
-      <x:c r="Q26" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R26" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S26" s="1" t="str">
+      <x:c r="O26" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P26" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q26" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -1912,45 +1752,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F27" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G27" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H27" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H27" s="7" t="n">
+        <x:v>3.86</x:v>
       </x:c>
       <x:c r="I27" s="7" t="n">
-        <x:v>3.86</x:v>
+        <x:v>10.93</x:v>
       </x:c>
       <x:c r="J27" s="7" t="n">
-        <x:v>2.8</x:v>
+        <x:v>26.33</x:v>
       </x:c>
       <x:c r="K27" s="7" t="n">
-        <x:v>10.93</x:v>
+        <x:v>3.24</x:v>
       </x:c>
       <x:c r="L27" s="7" t="n">
-        <x:v>26.33</x:v>
+        <x:v>1.44</x:v>
       </x:c>
       <x:c r="M27" s="7" t="n">
-        <x:v>3.24</x:v>
+        <x:v>3.92</x:v>
       </x:c>
       <x:c r="N27" s="7" t="n">
-        <x:v>1.44</x:v>
-      </x:c>
-      <x:c r="O27" s="7" t="n">
-        <x:v>3.92</x:v>
-      </x:c>
-      <x:c r="P27" s="7" t="n">
         <x:v>2.12</x:v>
       </x:c>
-      <x:c r="Q27" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R27" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S27" s="1" t="str">
+      <x:c r="O27" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P27" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q27" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -1971,45 +1805,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F28" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G28" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H28" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H28" s="7" t="n">
+        <x:v>1.48</x:v>
       </x:c>
       <x:c r="I28" s="7" t="n">
-        <x:v>1.48</x:v>
+        <x:v>31.87</x:v>
       </x:c>
       <x:c r="J28" s="7" t="n">
-        <x:v>2.7</x:v>
+        <x:v>32.53</x:v>
       </x:c>
       <x:c r="K28" s="7" t="n">
-        <x:v>31.87</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L28" s="7" t="n">
-        <x:v>32.53</x:v>
+        <x:v>2.19</x:v>
       </x:c>
       <x:c r="M28" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>2.69</x:v>
       </x:c>
       <x:c r="N28" s="7" t="n">
-        <x:v>2.19</x:v>
-      </x:c>
-      <x:c r="O28" s="7" t="n">
-        <x:v>2.69</x:v>
-      </x:c>
-      <x:c r="P28" s="7" t="n">
         <x:v>1.95</x:v>
       </x:c>
-      <x:c r="Q28" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R28" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S28" s="1" t="str">
+      <x:c r="O28" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P28" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q28" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -2030,45 +1858,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F29" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G29" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H29" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H29" s="7" t="n">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I29" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>13.44</x:v>
       </x:c>
       <x:c r="J29" s="7" t="n">
-        <x:v>2.68</x:v>
+        <x:v>35.82</x:v>
       </x:c>
       <x:c r="K29" s="7" t="n">
-        <x:v>13.44</x:v>
+        <x:v>3.42</x:v>
       </x:c>
       <x:c r="L29" s="7" t="n">
-        <x:v>35.82</x:v>
+        <x:v>2.33</x:v>
       </x:c>
       <x:c r="M29" s="7" t="n">
-        <x:v>3.42</x:v>
+        <x:v>4.29</x:v>
       </x:c>
       <x:c r="N29" s="7" t="n">
-        <x:v>2.33</x:v>
-      </x:c>
-      <x:c r="O29" s="7" t="n">
-        <x:v>4.29</x:v>
-      </x:c>
-      <x:c r="P29" s="7" t="n">
         <x:v>4.61</x:v>
       </x:c>
-      <x:c r="Q29" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R29" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S29" s="1" t="str">
+      <x:c r="O29" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P29" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q29" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -2089,45 +1911,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F30" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G30" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H30" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H30" s="7" t="n">
+        <x:v>1.58</x:v>
       </x:c>
       <x:c r="I30" s="7" t="n">
-        <x:v>1.58</x:v>
+        <x:v>13.49</x:v>
       </x:c>
       <x:c r="J30" s="7" t="n">
-        <x:v>2.77</x:v>
+        <x:v>32.84</x:v>
       </x:c>
       <x:c r="K30" s="7" t="n">
-        <x:v>13.49</x:v>
+        <x:v>2.32</x:v>
       </x:c>
       <x:c r="L30" s="7" t="n">
-        <x:v>32.84</x:v>
+        <x:v>1.16</x:v>
       </x:c>
       <x:c r="M30" s="7" t="n">
-        <x:v>2.32</x:v>
+        <x:v>4.23</x:v>
       </x:c>
       <x:c r="N30" s="7" t="n">
-        <x:v>1.16</x:v>
-      </x:c>
-      <x:c r="O30" s="7" t="n">
-        <x:v>4.23</x:v>
-      </x:c>
-      <x:c r="P30" s="7" t="n">
         <x:v>3.87</x:v>
       </x:c>
-      <x:c r="Q30" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R30" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S30" s="1" t="str">
+      <x:c r="O30" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P30" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q30" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -2148,45 +1964,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F31" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G31" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H31" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H31" s="7" t="n">
+        <x:v>4.98</x:v>
       </x:c>
       <x:c r="I31" s="7" t="n">
-        <x:v>4.98</x:v>
+        <x:v>11.21</x:v>
       </x:c>
       <x:c r="J31" s="7" t="n">
-        <x:v>3.32</x:v>
+        <x:v>23.42</x:v>
       </x:c>
       <x:c r="K31" s="7" t="n">
-        <x:v>11.21</x:v>
+        <x:v>3.9</x:v>
       </x:c>
       <x:c r="L31" s="7" t="n">
-        <x:v>23.42</x:v>
+        <x:v>2.18</x:v>
       </x:c>
       <x:c r="M31" s="7" t="n">
-        <x:v>3.9</x:v>
+        <x:v>2.88</x:v>
       </x:c>
       <x:c r="N31" s="7" t="n">
-        <x:v>2.18</x:v>
-      </x:c>
-      <x:c r="O31" s="7" t="n">
-        <x:v>2.88</x:v>
-      </x:c>
-      <x:c r="P31" s="7" t="n">
         <x:v>2.35</x:v>
       </x:c>
-      <x:c r="Q31" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R31" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S31" s="1" t="str">
+      <x:c r="O31" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P31" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q31" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -2207,45 +2017,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F32" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G32" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H32" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H32" s="7" t="n">
+        <x:v>4.36</x:v>
       </x:c>
       <x:c r="I32" s="7" t="n">
-        <x:v>4.36</x:v>
+        <x:v>20.76</x:v>
       </x:c>
       <x:c r="J32" s="7" t="n">
-        <x:v>0.81</x:v>
+        <x:v>32.75</x:v>
       </x:c>
       <x:c r="K32" s="7" t="n">
-        <x:v>20.76</x:v>
+        <x:v>4.52</x:v>
       </x:c>
       <x:c r="L32" s="7" t="n">
-        <x:v>32.75</x:v>
+        <x:v>2.79</x:v>
       </x:c>
       <x:c r="M32" s="7" t="n">
-        <x:v>4.52</x:v>
+        <x:v>4.04</x:v>
       </x:c>
       <x:c r="N32" s="7" t="n">
-        <x:v>2.79</x:v>
-      </x:c>
-      <x:c r="O32" s="7" t="n">
-        <x:v>4.04</x:v>
-      </x:c>
-      <x:c r="P32" s="7" t="n">
         <x:v>3.26</x:v>
       </x:c>
-      <x:c r="Q32" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R32" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S32" s="1" t="str">
+      <x:c r="O32" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P32" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q32" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -2266,45 +2070,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F33" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G33" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H33" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H33" s="7" t="n">
+        <x:v>5.9</x:v>
       </x:c>
       <x:c r="I33" s="7" t="n">
-        <x:v>5.9</x:v>
+        <x:v>25.2</x:v>
       </x:c>
       <x:c r="J33" s="7" t="n">
-        <x:v>2.44</x:v>
+        <x:v>39.62</x:v>
       </x:c>
       <x:c r="K33" s="7" t="n">
-        <x:v>25.2</x:v>
+        <x:v>5.97</x:v>
       </x:c>
       <x:c r="L33" s="7" t="n">
-        <x:v>39.62</x:v>
+        <x:v>2.33</x:v>
       </x:c>
       <x:c r="M33" s="7" t="n">
-        <x:v>5.97</x:v>
+        <x:v>4.96</x:v>
       </x:c>
       <x:c r="N33" s="7" t="n">
-        <x:v>2.33</x:v>
-      </x:c>
-      <x:c r="O33" s="7" t="n">
-        <x:v>4.96</x:v>
-      </x:c>
-      <x:c r="P33" s="7" t="n">
         <x:v>3.21</x:v>
       </x:c>
-      <x:c r="Q33" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R33" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S33" s="1" t="str">
+      <x:c r="O33" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P33" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q33" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -2325,45 +2123,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F34" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G34" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H34" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H34" s="7" t="n">
+        <x:v>5.07</x:v>
       </x:c>
       <x:c r="I34" s="7" t="n">
-        <x:v>5.07</x:v>
+        <x:v>11.98</x:v>
       </x:c>
       <x:c r="J34" s="7" t="n">
-        <x:v>2.93</x:v>
+        <x:v>29.61</x:v>
       </x:c>
       <x:c r="K34" s="7" t="n">
-        <x:v>11.98</x:v>
+        <x:v>4.81</x:v>
       </x:c>
       <x:c r="L34" s="7" t="n">
-        <x:v>29.61</x:v>
+        <x:v>2.04</x:v>
       </x:c>
       <x:c r="M34" s="7" t="n">
-        <x:v>4.81</x:v>
+        <x:v>3.93</x:v>
       </x:c>
       <x:c r="N34" s="7" t="n">
-        <x:v>2.04</x:v>
-      </x:c>
-      <x:c r="O34" s="7" t="n">
-        <x:v>3.93</x:v>
-      </x:c>
-      <x:c r="P34" s="7" t="n">
         <x:v>3.73</x:v>
       </x:c>
-      <x:c r="Q34" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R34" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S34" s="1" t="str">
+      <x:c r="O34" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P34" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q34" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -2384,45 +2176,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F35" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G35" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H35" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H35" s="7" t="n">
+        <x:v>4.48</x:v>
       </x:c>
       <x:c r="I35" s="7" t="n">
+        <x:v>9.98</x:v>
+      </x:c>
+      <x:c r="J35" s="7" t="n">
+        <x:v>30.97</x:v>
+      </x:c>
+      <x:c r="K35" s="7" t="n">
         <x:v>4.48</x:v>
       </x:c>
-      <x:c r="J35" s="7" t="n">
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="K35" s="7" t="n">
-        <x:v>9.98</x:v>
-      </x:c>
       <x:c r="L35" s="7" t="n">
-        <x:v>30.97</x:v>
+        <x:v>2.19</x:v>
       </x:c>
       <x:c r="M35" s="7" t="n">
-        <x:v>4.48</x:v>
+        <x:v>3.79</x:v>
       </x:c>
       <x:c r="N35" s="7" t="n">
-        <x:v>2.19</x:v>
-      </x:c>
-      <x:c r="O35" s="7" t="n">
-        <x:v>3.79</x:v>
-      </x:c>
-      <x:c r="P35" s="7" t="n">
         <x:v>4.22</x:v>
       </x:c>
-      <x:c r="Q35" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R35" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S35" s="1" t="str">
+      <x:c r="O35" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P35" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q35" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -2443,45 +2229,39 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F36" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G36" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H36" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H36" s="7" t="n">
+        <x:v>4.57</x:v>
       </x:c>
       <x:c r="I36" s="7" t="n">
-        <x:v>4.57</x:v>
+        <x:v>18.95</x:v>
       </x:c>
       <x:c r="J36" s="7" t="n">
-        <x:v>2.88</x:v>
+        <x:v>36.71</x:v>
       </x:c>
       <x:c r="K36" s="7" t="n">
-        <x:v>18.95</x:v>
+        <x:v>5.25</x:v>
       </x:c>
       <x:c r="L36" s="7" t="n">
-        <x:v>36.71</x:v>
+        <x:v>2.17</x:v>
       </x:c>
       <x:c r="M36" s="7" t="n">
-        <x:v>5.25</x:v>
+        <x:v>4.87</x:v>
       </x:c>
       <x:c r="N36" s="7" t="n">
-        <x:v>2.17</x:v>
-      </x:c>
-      <x:c r="O36" s="7" t="n">
-        <x:v>4.87</x:v>
-      </x:c>
-      <x:c r="P36" s="7" t="n">
         <x:v>1.98</x:v>
       </x:c>
-      <x:c r="Q36" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R36" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S36" s="1" t="str">
+      <x:c r="O36" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P36" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q36" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
@@ -2502,64 +2282,58 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F37" s="1" t="str">
-        <x:v>demo</x:v>
+        <x:v>real</x:v>
       </x:c>
       <x:c r="G37" s="1" t="str">
-        <x:v>DEMO-SUSP-01</x:v>
-      </x:c>
-      <x:c r="H37" s="1" t="str">
-        <x:v>mg/g_dw</x:v>
+        <x:v>mg/g_dw</x:v>
+      </x:c>
+      <x:c r="H37" s="7" t="n">
+        <x:v>1.47</x:v>
       </x:c>
       <x:c r="I37" s="7" t="n">
-        <x:v>1.47</x:v>
+        <x:v>30.25</x:v>
       </x:c>
       <x:c r="J37" s="7" t="n">
-        <x:v>1.04</x:v>
+        <x:v>28.55</x:v>
       </x:c>
       <x:c r="K37" s="7" t="n">
-        <x:v>30.25</x:v>
+        <x:v>4.52</x:v>
       </x:c>
       <x:c r="L37" s="7" t="n">
-        <x:v>28.55</x:v>
+        <x:v>2.68</x:v>
       </x:c>
       <x:c r="M37" s="7" t="n">
-        <x:v>4.52</x:v>
+        <x:v>2.6</x:v>
       </x:c>
       <x:c r="N37" s="7" t="n">
-        <x:v>2.68</x:v>
-      </x:c>
-      <x:c r="O37" s="7" t="n">
-        <x:v>2.6</x:v>
-      </x:c>
-      <x:c r="P37" s="7" t="n">
         <x:v>3.23</x:v>
       </x:c>
-      <x:c r="Q37" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="R37" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S37" s="1" t="str">
+      <x:c r="O37" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P37" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q37" s="1" t="str">
         <x:v>전 항목 합성. 실제 산지/품종 특성 아님.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="F2:F1501">
-      <x:formula1>"demo,real"</x:formula1>
+      <x:formula1>"real"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="H2:H1501">
+    <x:dataValidation type="list" sqref="G2:G1501">
       <x:formula1>"mg/g_dw"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="between" sqref="M2:P1501">
+    <x:dataValidation type="decimal" operator="between" sqref="K2:N1501">
       <x:formula1>0</x:formula1>
       <x:formula2>10</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91d91eceacb84501"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc7e858d17ae4423"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2607,7 +2381,7 @@
         <x:v>단위</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>glutamate / glutamine / theanine / caffeine: mg/g 건물 기준. unit=mg/g_dw 고정.</x:v>
+        <x:v>glutamate / theanine / caffeine: mg/g 건물 기준. unit=mg/g_dw 고정.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
@@ -2615,7 +2389,7 @@
         <x:v>성분 구분</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>glutamate=글루탐산(Glu), glutamine=글루타민(Gln). 서로 대체하거나 같은 열에 섞지 않습니다.</x:v>
+        <x:v>glutamate=글루탐산(Glu), theanine=테아닌, caffeine=카페인. 세 성분만 입력합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
@@ -2647,15 +2421,15 @@
         <x:v>data_type</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>demo=합성 / real=실측. 예제를 실제 측정치로 오인하여 real로 변경하지 않습니다. 화면에서 두 집단을 분리합니다.</x:v>
+        <x:v>real로 고정합니다. 현재 수치는 가상입니다. data_type은 관리용 구분이며 측정 여부를 증명하지 않습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
       <x:c r="A11" s="11" t="str">
-        <x:v>protocol_id</x:v>
+        <x:v>분석 대상</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>분말량·물량·수질·온도·분산시간·평가온도·척도·패널 기준을 문서로 정의하고 동일 조건에 같은 ID를 부여합니다.</x:v>
+        <x:v>등록된 전체 시료를 학습합니다. 서로 비교 가능한 조제·평가 조건으로 데이터를 관리합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
@@ -2679,7 +2453,7 @@
         <x:v>notes</x:v>
       </x:c>
       <x:c r="B14" s="9" t="str">
-        <x:v>분석법, 수분보정, 결측 사유, 원자료 위치 등을 기록합니다.</x:v>
+        <x:v>현재 행은 가상임을 표시했습니다. 실측값으로 교체할 때 실제 분석법·측정일·원자료 위치로 갱신합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
@@ -2687,7 +2461,7 @@
         <x:v>결측</x:v>
       </x:c>
       <x:c r="B15" s="9" t="str">
-        <x:v>Glu 또는 Gln 하나는 비워둘 수 있습니다. 선택 성분이 결측인 행은 모델에서 제외됩니다. 기타 필수 숫자는 누락 시 CSV 전체를 거부합니다.</x:v>
+        <x:v>글루탐산·테아닌·카페인과 네 관능값은 필수입니다. 숫자 누락 시 CSV 전체를 거부합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="42" customHeight="1">
@@ -2711,7 +2485,7 @@
         <x:v>생성 범위</x:v>
       </x:c>
       <x:c r="B18" s="9" t="str">
-        <x:v>Glu 1–6, Gln 0.4–3.4, 테아닌 6–32, 카페인 18–40 mg/g DW. 문헌 참값/산지 평균이 아닌 예제 설계 범위.</x:v>
+        <x:v>Glu 1–6, 테아닌 6–32, 카페인 18–40 mg/g DW. 문헌 참값/산지 평균이 아닌 예제 설계 범위.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="42" customHeight="1">
@@ -3039,13 +2813,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B063BA9-0FF8-48EB-9DFF-AAF86B4BAB9F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{077A51D0-54C9-49F0-A052-26AF6FACD56B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B700E2C7-DE49-40E9-992E-29279E54913B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BB212B2-22CA-4751-9ED1-CF171DAD2870}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FA3E865-6F89-4D81-8F38-B036E19AD465}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7251D1C-BE1A-4BA2-BEBD-2CC75CE5B27E}"/>
 </file>
--- a/matcha_library.xlsx
+++ b/matcha_library.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data" sheetId="1" r:id="R1e50be06358041d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용안내" sheetId="2" r:id="Re92b54df690d408f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data" sheetId="1" r:id="R8f153302b1c14de4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용안내" sheetId="2" r:id="Rcfda35e617584868"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -427,7 +427,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F2" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G2" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -480,7 +480,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F3" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G3" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -533,7 +533,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F4" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G4" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -586,7 +586,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G5" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -639,7 +639,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F6" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G6" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -692,7 +692,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F7" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G7" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -745,7 +745,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F8" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G8" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -798,7 +798,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F9" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G9" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -851,7 +851,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F10" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G10" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -904,7 +904,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F11" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G11" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -957,7 +957,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F12" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G12" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -1010,7 +1010,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F13" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G13" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -1063,7 +1063,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F14" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G14" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -1116,7 +1116,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F15" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G15" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -1169,7 +1169,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F16" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G16" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -1222,7 +1222,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F17" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G17" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -1275,7 +1275,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F18" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G18" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F19" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G19" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -1381,7 +1381,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F20" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G20" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -1434,7 +1434,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F21" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G21" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -1487,7 +1487,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F22" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G22" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -1540,7 +1540,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F23" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G23" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -1593,7 +1593,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F24" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G24" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -1646,7 +1646,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F25" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G25" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -1699,7 +1699,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F26" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G26" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -1752,7 +1752,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F27" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G27" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -1805,7 +1805,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F28" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G28" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -1858,7 +1858,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F29" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G29" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -1911,7 +1911,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F30" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G30" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -1964,7 +1964,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F31" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G31" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -2017,7 +2017,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F32" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G32" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -2070,7 +2070,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F33" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G33" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -2123,7 +2123,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F34" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G34" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -2176,7 +2176,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F35" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G35" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -2229,7 +2229,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F36" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G36" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -2282,7 +2282,7 @@
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="F37" s="1" t="str">
-        <x:v>real</x:v>
+        <x:v>demo</x:v>
       </x:c>
       <x:c r="G37" s="1" t="str">
         <x:v>mg/g_dw</x:v>
@@ -2320,9 +2320,6 @@
     </x:row>
   </x:sheetData>
   <x:dataValidations count="3">
-    <x:dataValidation type="list" sqref="F2:F1501">
-      <x:formula1>"real"</x:formula1>
-    </x:dataValidation>
     <x:dataValidation type="list" sqref="G2:G1501">
       <x:formula1>"mg/g_dw"</x:formula1>
     </x:dataValidation>
@@ -2330,10 +2327,13 @@
       <x:formula1>0</x:formula1>
       <x:formula2>10</x:formula2>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="F2:F1501">
+      <x:formula1>"demo,real"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc7e858d17ae4423"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bc55c40f5884843"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2421,7 +2421,7 @@
         <x:v>data_type</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>real로 고정합니다. 현재 수치는 가상입니다. data_type은 관리용 구분이며 측정 여부를 증명하지 않습니다.</x:v>
+        <x:v>demo=가상 예제, real=실측값. 실측 전환 시 성분·관능값과 notes를 함께 갱신하세요.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
@@ -2429,7 +2429,7 @@
         <x:v>분석 대상</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>등록된 전체 시료를 학습합니다. 서로 비교 가능한 조제·평가 조건으로 데이터를 관리합니다.</x:v>
+        <x:v>실측 행이 있으면 real만 학습합니다. 실측이 없을 때만 demo로 작동하며 두 유형은 섞지 않습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
@@ -2453,7 +2453,7 @@
         <x:v>notes</x:v>
       </x:c>
       <x:c r="B14" s="9" t="str">
-        <x:v>현재 행은 가상임을 표시했습니다. 실측값으로 교체할 때 실제 분석법·측정일·원자료 위치로 갱신합니다.</x:v>
+        <x:v>실측 시 분석법·조제 조건·측정일·원자료 위치를 기록하세요. 가상 행은 합성 표시를 유지합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
@@ -2541,7 +2541,7 @@
         <x:v>문헌 링크</x:v>
       </x:c>
       <x:c r="B25" s="9" t="str">
-        <x:v>https://portal.fis.tum.de/de/publications/molecular-and-sensory-studies-on-the-umami-taste-of-japanese-gree/</x:v>
+        <x:v>https://doi.org/10.1021/jf0525232</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="42" customHeight="1">
@@ -2813,13 +2813,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{077A51D0-54C9-49F0-A052-26AF6FACD56B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D34890A-47B4-4F73-9DCB-02326AF60214}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BB212B2-22CA-4751-9ED1-CF171DAD2870}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{635ED898-1AD9-44AF-B9D1-0DE623F67F06}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7251D1C-BE1A-4BA2-BEBD-2CC75CE5B27E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56F68988-5ED8-4074-969A-61ACE40FF497}"/>
 </file>